--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.77032470470606</v>
+        <v>3.700177764514735</v>
       </c>
       <c r="D2" t="n">
-        <v>22.71104142510672</v>
+        <v>3.690544231579843</v>
       </c>
       <c r="E2" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F2" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.40880240487104</v>
+        <v>5.591430390791544</v>
       </c>
       <c r="D3" t="n">
-        <v>34.34614170089834</v>
+        <v>5.581248026395981</v>
       </c>
       <c r="E3" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F3" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.22516979620022</v>
+        <v>5.561590091882536</v>
       </c>
       <c r="D4" t="n">
-        <v>34.27626611169906</v>
+        <v>5.569893243151097</v>
       </c>
       <c r="E4" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F4" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.088566582348546</v>
+        <v>0.6643920696316388</v>
       </c>
       <c r="D5" t="n">
-        <v>4.149950887223799</v>
+        <v>0.6743670191738673</v>
       </c>
       <c r="E5" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F5" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.75907328258717</v>
+        <v>5.648349408420414</v>
       </c>
       <c r="D6" t="n">
-        <v>34.69885604620818</v>
+        <v>5.638564107508829</v>
       </c>
       <c r="E6" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F6" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.93521914168611</v>
+        <v>3.401973110523993</v>
       </c>
       <c r="D7" t="n">
-        <v>20.93168062098257</v>
+        <v>3.401398100909668</v>
       </c>
       <c r="E7" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F7" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.939101396003</v>
+        <v>3.077603976850488</v>
       </c>
       <c r="D8" t="n">
-        <v>19.08224652016135</v>
+        <v>3.10086505952622</v>
       </c>
       <c r="E8" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F8" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.25183633923287</v>
+        <v>4.265923405125341</v>
       </c>
       <c r="D9" t="n">
-        <v>26.47574093446296</v>
+        <v>4.302307901850232</v>
       </c>
       <c r="E9" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F9" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74114164200232</v>
+        <v>5.320435516825377</v>
       </c>
       <c r="D10" t="n">
-        <v>32.75110647542769</v>
+        <v>5.322054802257</v>
       </c>
       <c r="E10" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F10" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.35718685049892</v>
+        <v>6.395542863206074</v>
       </c>
       <c r="D11" t="n">
-        <v>39.61509276746666</v>
+        <v>6.437452574713332</v>
       </c>
       <c r="E11" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F11" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.46505871912756</v>
+        <v>2.350572041858228</v>
       </c>
       <c r="D12" t="n">
-        <v>14.38575300476907</v>
+        <v>2.337684863274973</v>
       </c>
       <c r="E12" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F12" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.31474316606938</v>
+        <v>4.276145764486275</v>
       </c>
       <c r="D13" t="n">
-        <v>26.55820056191143</v>
+        <v>4.315707591310607</v>
       </c>
       <c r="E13" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F13" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.50627442959043</v>
+        <v>2.844769594808445</v>
       </c>
       <c r="D14" t="n">
-        <v>17.60007132488502</v>
+        <v>2.860011590293816</v>
       </c>
       <c r="E14" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F14" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.68730737641501</v>
+        <v>4.336687448667439</v>
       </c>
       <c r="D15" t="n">
-        <v>26.86021446782624</v>
+        <v>4.364784851021764</v>
       </c>
       <c r="E15" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F15" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.69097530858255</v>
+        <v>5.312283487644665</v>
       </c>
       <c r="D16" t="n">
-        <v>32.82127065093551</v>
+        <v>5.333456480777021</v>
       </c>
       <c r="E16" t="n">
-        <v>9.145489051056064</v>
+        <v>1.48614197079661</v>
       </c>
       <c r="F16" t="n">
-        <v>9.162663339050878</v>
+        <v>1.488932792595768</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
